--- a/src/assets/template-invoice.xlsx
+++ b/src/assets/template-invoice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HSD\Desktop\stonehub\src\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FD07EE6-F177-416B-B44B-6FEEA1F48B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED90B62E-E5EB-4705-84B6-0839B7E4EA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>THÔNG TIN ĐỀ NGHỊ XUẤT HÓA ĐƠN</t>
   </si>
@@ -83,9 +83,6 @@
   </si>
   <si>
     <t>Địa chỉ: Số 6D Phan Kế Bính, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam</t>
-  </si>
-  <si>
-    <t>SĐT: 0333899266</t>
   </si>
   <si>
     <t xml:space="preserve">       Vũ Thanh Thùy</t>
@@ -706,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
@@ -745,14 +742,14 @@
     <row r="4" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="C4" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
     </row>
     <row r="5" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
@@ -770,60 +767,60 @@
     </row>
     <row r="7" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="23"/>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
       <c r="E7" s="23"/>
     </row>
-    <row r="8" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-    </row>
-    <row r="10" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+    <row r="9" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B9" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C9" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D9" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E9" s="17" t="s">
         <v>3</v>
       </c>
     </row>
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>1</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="18">
+        <v>481.0256</v>
+      </c>
+      <c r="D10" s="9">
+        <v>380000</v>
+      </c>
+      <c r="E10" s="10">
+        <f>C10*D10</f>
+        <v>182789728</v>
+      </c>
+    </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>1</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="18">
-        <v>481.0256</v>
-      </c>
-      <c r="D11" s="9">
-        <v>380000</v>
-      </c>
-      <c r="E11" s="10">
-        <f>C11*D11</f>
-        <v>182789728</v>
-      </c>
+      <c r="A11" s="11">
+        <v>2</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="10"/>
@@ -832,7 +829,7 @@
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="10"/>
@@ -841,7 +838,7 @@
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="10"/>
@@ -850,7 +847,7 @@
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B15" s="12"/>
       <c r="C15" s="10"/>
@@ -859,25 +856,25 @@
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B16" s="12"/>
-      <c r="C16" s="10"/>
+      <c r="C16" s="19"/>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B17" s="12"/>
-      <c r="C17" s="19"/>
+      <c r="C17" s="10"/>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18" s="12"/>
       <c r="C18" s="10"/>
@@ -886,7 +883,7 @@
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="10"/>
@@ -894,85 +891,75 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="11">
+      <c r="A20" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-    </row>
-    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="14">
+        <f>E10-E19-E18-E17-E16</f>
+        <v>182789728</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="30" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
       <c r="D21" s="32"/>
-      <c r="E21" s="14">
-        <f>E11-E20-E19-E18-E17</f>
-        <v>182789728</v>
-      </c>
+      <c r="E21" s="13"/>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="32"/>
+      <c r="A22" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="29"/>
       <c r="E22" s="13"/>
     </row>
-    <row r="23" spans="1:5" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="13"/>
+    <row r="23" spans="1:5" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
     </row>
     <row r="24" spans="1:5" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>5</v>
+      <c r="A24" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D24" s="21"/>
       <c r="E24" s="21"/>
     </row>
-    <row r="25" spans="1:5" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D30" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" s="20"/>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D29" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A23:D23"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="C23:E23"/>
     <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/src/assets/template-invoice.xlsx
+++ b/src/assets/template-invoice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HSD\Desktop\stonehub\src\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED90B62E-E5EB-4705-84B6-0839B7E4EA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C912FEC5-C3E5-4A76-9764-E00F57ECB96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -343,11 +343,32 @@
     <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -361,32 +382,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -715,13 +715,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
     </row>
     <row r="2" spans="1:5" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
@@ -731,48 +731,48 @@
       <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
     </row>
     <row r="5" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
     </row>
     <row r="6" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
     </row>
     <row r="9" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
@@ -798,7 +798,7 @@
       <c r="B10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="31">
         <v>481.0256</v>
       </c>
       <c r="D10" s="9">
@@ -814,7 +814,7 @@
         <v>2</v>
       </c>
       <c r="B11" s="12"/>
-      <c r="C11" s="10"/>
+      <c r="C11" s="32"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
     </row>
@@ -823,7 +823,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="12"/>
-      <c r="C12" s="10"/>
+      <c r="C12" s="32"/>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
     </row>
@@ -832,7 +832,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="12"/>
-      <c r="C13" s="10"/>
+      <c r="C13" s="32"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
     </row>
@@ -841,7 +841,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="12"/>
-      <c r="C14" s="10"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
     </row>
@@ -850,7 +850,7 @@
         <v>6</v>
       </c>
       <c r="B15" s="12"/>
-      <c r="C15" s="10"/>
+      <c r="C15" s="32"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
     </row>
@@ -859,7 +859,7 @@
         <v>7</v>
       </c>
       <c r="B16" s="12"/>
-      <c r="C16" s="19"/>
+      <c r="C16" s="32"/>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
     </row>
@@ -868,7 +868,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="12"/>
-      <c r="C17" s="10"/>
+      <c r="C17" s="32"/>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
     </row>
@@ -877,7 +877,7 @@
         <v>9</v>
       </c>
       <c r="B18" s="12"/>
-      <c r="C18" s="10"/>
+      <c r="C18" s="32"/>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
     </row>
@@ -886,80 +886,80 @@
         <v>10</v>
       </c>
       <c r="B19" s="12"/>
-      <c r="C19" s="10"/>
+      <c r="C19" s="32"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="32"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="26"/>
       <c r="E20" s="14">
         <f>E10-E19-E18-E17-E16</f>
         <v>182789728</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="32"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="26"/>
       <c r="E21" s="13"/>
     </row>
     <row r="22" spans="1:5" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="29"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="23"/>
       <c r="E22" s="13"/>
     </row>
     <row r="23" spans="1:5" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
     </row>
     <row r="24" spans="1:5" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D29" s="20" t="s">
+      <c r="D29" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="E29" s="20"/>
+      <c r="E29" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A20:D20"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
